--- a/data/Mörel-Filet/investment_decision/Filet_SFH_until_2004_investment_decision.xlsx
+++ b/data/Mörel-Filet/investment_decision/Filet_SFH_until_2004_investment_decision.xlsx
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>348.8621015651902</v>
+        <v>94.36372907277476</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>51194.85639929007</v>
       </c>
       <c r="F2" t="n">
-        <v>346.6789350623211</v>
+        <v>94.36372907277476</v>
       </c>
       <c r="G2" t="n">
         <v>51194.85639929007</v>
       </c>
       <c r="H2" t="n">
-        <v>346.6789350623211</v>
+        <v>94.36372907277477</v>
       </c>
       <c r="I2" t="n">
         <v>51194.85639929007</v>
       </c>
       <c r="J2" t="n">
-        <v>348.8009056987877</v>
+        <v>94.36372907277476</v>
       </c>
       <c r="K2" t="n">
         <v>51194.85639929007</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>348.8621015651902</v>
+        <v>158.4094731434923</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>51194.85639929007</v>
       </c>
       <c r="F3" t="n">
-        <v>346.6789350623211</v>
+        <v>161.778947191716</v>
       </c>
       <c r="G3" t="n">
         <v>51194.85639929007</v>
       </c>
       <c r="H3" t="n">
-        <v>346.6789350623211</v>
+        <v>162.2357639942932</v>
       </c>
       <c r="I3" t="n">
         <v>51194.85639929007</v>
       </c>
       <c r="J3" t="n">
-        <v>348.8009056987876</v>
+        <v>158.4072435535407</v>
       </c>
       <c r="K3" t="n">
         <v>51194.85639929007</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>348.8621015651902</v>
+        <v>158.4094731434923</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>51194.85639929007</v>
       </c>
       <c r="F4" t="n">
-        <v>346.6789350623211</v>
+        <v>161.778947191716</v>
       </c>
       <c r="G4" t="n">
         <v>51194.85639929007</v>
       </c>
       <c r="H4" t="n">
-        <v>346.6789350623211</v>
+        <v>162.2357639942932</v>
       </c>
       <c r="I4" t="n">
         <v>51194.85639929007</v>
       </c>
       <c r="J4" t="n">
-        <v>348.8009056987876</v>
+        <v>158.4072435535407</v>
       </c>
       <c r="K4" t="n">
         <v>51194.85639929007</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>348.8621015651902</v>
+        <v>158.4094731434923</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>51194.85639929007</v>
       </c>
       <c r="F5" t="n">
-        <v>346.6789350623211</v>
+        <v>161.778947191716</v>
       </c>
       <c r="G5" t="n">
         <v>51194.85639929007</v>
       </c>
       <c r="H5" t="n">
-        <v>346.6789350623211</v>
+        <v>162.2357639942932</v>
       </c>
       <c r="I5" t="n">
         <v>51194.85639929007</v>
       </c>
       <c r="J5" t="n">
-        <v>348.8009056987876</v>
+        <v>158.4072435535407</v>
       </c>
       <c r="K5" t="n">
         <v>51194.85639929007</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>348.8621015651902</v>
+        <v>158.4094731434923</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>51194.85639929007</v>
       </c>
       <c r="F6" t="n">
-        <v>346.6789350623211</v>
+        <v>161.778947191716</v>
       </c>
       <c r="G6" t="n">
         <v>51194.85639929007</v>
       </c>
       <c r="H6" t="n">
-        <v>346.6789350623211</v>
+        <v>162.2357639942932</v>
       </c>
       <c r="I6" t="n">
         <v>51194.85639929007</v>
       </c>
       <c r="J6" t="n">
-        <v>348.8009056987876</v>
+        <v>158.4072435535407</v>
       </c>
       <c r="K6" t="n">
         <v>51194.85639929007</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>76.79228459893511</v>
+        <v>63.00756943820225</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>76.79228459893511</v>
+        <v>63.00756943820225</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>44.09674459709053</v>
+        <v>36.18109178169157</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>44.09674459709053</v>
+        <v>36.18109178169157</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>76.79228459893511</v>
+        <v>63.00756943820225</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>76.79228459893511</v>
+        <v>63.00756943820225</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>57.02556827203952</v>
+        <v>46.78910741383644</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>57.02556827203952</v>
+        <v>46.78910741383644</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>76.79228459893511</v>
+        <v>63.00756943820225</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>76.79228459893511</v>
+        <v>63.00756943820225</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>62.78332747653547</v>
+        <v>51.51331134630751</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>62.78332747653547</v>
+        <v>51.51331134630751</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>76.79228459893511</v>
+        <v>63.00756943820225</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>76.79228459893511</v>
+        <v>63.00756943820225</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>65.93842927862579</v>
+        <v>54.10205182874081</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>65.93842927862579</v>
+        <v>54.10205182874081</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>76.79228459893511</v>
+        <v>63.00756943820225</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>76.79228459893511</v>
+        <v>63.00756943820225</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>67.89737865539203</v>
+        <v>55.70935703560053</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>67.89737865539203</v>
+        <v>55.70935703560053</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.009754524804705882</v>
+        <v>0.008482195482352942</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.009754524804705882</v>
+        <v>0.008482195482352942</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.009754524804705882</v>
+        <v>0.008482195482352942</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.009754524804705882</v>
+        <v>0.008482195482352942</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.009754524804705884</v>
+        <v>0.008968129400109577</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.009754524804705884</v>
+        <v>0.008906305256470588</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.009754524804705884</v>
+        <v>0.009078664530749687</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.009754524804705884</v>
+        <v>0.009084216559095921</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01145096390117647</v>
+        <v>0.009655080564705879</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01145096390117647</v>
+        <v>0.009655080564705883</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01145096390117647</v>
+        <v>0.009668767759394781</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01145096390117647</v>
+        <v>0.009658540040460096</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01145096390117647</v>
+        <v>0.009655080564705877</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01145096390117647</v>
+        <v>0.009655080564705883</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01145096390117647</v>
+        <v>0.009668767759394781</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01145096390117647</v>
+        <v>0.009658540040460096</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01145096390117647</v>
+        <v>0.009655080564705879</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01145096390117647</v>
+        <v>0.009655080564705883</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01145096390117647</v>
+        <v>0.009668767759394781</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01145096390117647</v>
+        <v>0.009658540040460096</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1.467570809102581</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>7.570359468000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.427396869894241</v>
       </c>
       <c r="G19" t="n">
         <v>7.570359468000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1.422069578547471</v>
       </c>
       <c r="I19" t="n">
         <v>7.570359468000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.456242767015872</v>
       </c>
       <c r="K19" t="n">
         <v>7.570359468000001</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1.467570809102581</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>7.570359468000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.427396869894241</v>
       </c>
       <c r="G20" t="n">
         <v>7.570359468000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.422069578547471</v>
       </c>
       <c r="I20" t="n">
         <v>7.570359468000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.456242767015872</v>
       </c>
       <c r="K20" t="n">
         <v>7.570359468000001</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1.467570809102581</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>7.570359468000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.427396869894241</v>
       </c>
       <c r="G21" t="n">
         <v>7.570359468000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.422069578547471</v>
       </c>
       <c r="I21" t="n">
         <v>7.570359468000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.456242767015872</v>
       </c>
       <c r="K21" t="n">
         <v>7.570359468000001</v>
@@ -1557,7 +1557,7 @@
         <v>7.570359468000001</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.01135475289762095</v>
       </c>
       <c r="K30" t="n">
         <v>7.570359468000001</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.05282975250000239</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>7.570359468000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.05282975250000058</v>
       </c>
       <c r="G31" t="n">
         <v>7.570359468000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.04555843032152308</v>
       </c>
       <c r="I31" t="n">
         <v>7.570359468000001</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.05099190600557548</v>
       </c>
       <c r="K31" t="n">
         <v>7.570359468000001</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>10.18636867127234</v>
+        <v>8.210769408770783</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>78.73510653663386</v>
       </c>
       <c r="F53" t="n">
-        <v>9.70303962942968</v>
+        <v>8.074285066454092</v>
       </c>
       <c r="G53" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="H53" t="n">
-        <v>9.543791299197293</v>
+        <v>8.0336580158405</v>
       </c>
       <c r="I53" t="n">
         <v>31.29582872385541</v>
       </c>
       <c r="J53" t="n">
-        <v>10.18636867127233</v>
+        <v>8.19665536317191</v>
       </c>
       <c r="K53" t="n">
         <v>31.29582872385541</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>25.30096407773822</v>
+        <v>25.43023959334102</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>78.73510653663386</v>
       </c>
       <c r="F54" t="n">
-        <v>24.14785703368869</v>
+        <v>23.83601370140675</v>
       </c>
       <c r="G54" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="H54" t="n">
-        <v>24.14785703368869</v>
+        <v>23.85316646352484</v>
       </c>
       <c r="I54" t="n">
         <v>37.07638252847705</v>
       </c>
       <c r="J54" t="n">
-        <v>25.3009386854314</v>
+        <v>25.43009610907371</v>
       </c>
       <c r="K54" t="n">
         <v>37.07638252847705</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>25.98396023125199</v>
+        <v>25.70949517913206</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>78.73510653663386</v>
       </c>
       <c r="F55" t="n">
-        <v>25.46655695654781</v>
+        <v>25.25738375909173</v>
       </c>
       <c r="G55" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="H55" t="n">
-        <v>25.46655695654781</v>
+        <v>25.24609444356715</v>
       </c>
       <c r="I55" t="n">
         <v>40.79562598639043</v>
       </c>
       <c r="J55" t="n">
-        <v>25.98392119500248</v>
+        <v>25.70941146148892</v>
       </c>
       <c r="K55" t="n">
         <v>40.79562598639043</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>25.93640213568806</v>
+        <v>25.29353002121453</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>78.73510653663386</v>
       </c>
       <c r="F56" t="n">
-        <v>24.63842744618301</v>
+        <v>24.75198788038901</v>
       </c>
       <c r="G56" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="H56" t="n">
-        <v>24.63842744618301</v>
+        <v>24.75198788038901</v>
       </c>
       <c r="I56" t="n">
         <v>43.38101700506569</v>
       </c>
       <c r="J56" t="n">
-        <v>25.9363938062709</v>
+        <v>25.29344630357139</v>
       </c>
       <c r="K56" t="n">
         <v>43.38101700506569</v>
@@ -2715,7 +2715,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>1.832989050051336</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2729,19 +2729,19 @@
         <v>78.73510653663386</v>
       </c>
       <c r="F62" t="n">
-        <v>1.881147134673449</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="H62" t="n">
-        <v>1.881147134673449</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="J62" t="n">
-        <v>1.834338958869039</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>78.73510653663386</v>
@@ -2752,7 +2752,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>1.832989050051336</v>
+        <v>0</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,19 +2766,19 @@
         <v>78.73510653663386</v>
       </c>
       <c r="F63" t="n">
-        <v>2.364476176516106</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="H63" t="n">
-        <v>2.523724506748493</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="J63" t="n">
-        <v>1.834338958869039</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>78.73510653663386</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>6.718393643585448</v>
+        <v>3.17008197663934</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>78.73510653663386</v>
       </c>
       <c r="F64" t="n">
-        <v>7.919658772257082</v>
+        <v>4.734841202480453</v>
       </c>
       <c r="G64" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="H64" t="n">
-        <v>7.919658772257082</v>
+        <v>4.713230195449099</v>
       </c>
       <c r="I64" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="J64" t="n">
-        <v>6.719768944709964</v>
+        <v>3.17012785911405</v>
       </c>
       <c r="K64" t="n">
         <v>78.73510653663386</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>9.035397490071682</v>
+        <v>5.890826390848306</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>78.73510653663386</v>
       </c>
       <c r="F65" t="n">
-        <v>9.600958849397971</v>
+        <v>6.313471144795472</v>
       </c>
       <c r="G65" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="H65" t="n">
-        <v>9.600958849397971</v>
+        <v>6.320302215406802</v>
       </c>
       <c r="I65" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="J65" t="n">
-        <v>9.036786435138886</v>
+        <v>5.890812506698841</v>
       </c>
       <c r="K65" t="n">
         <v>78.73510653663386</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>13.87338999139935</v>
+        <v>9.118092802812532</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>78.73510653663386</v>
       </c>
       <c r="F66" t="n">
-        <v>15.21952276552651</v>
+        <v>9.627972179012001</v>
       </c>
       <c r="G66" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="H66" t="n">
-        <v>15.21952276552651</v>
+        <v>9.623422321433624</v>
       </c>
       <c r="I66" t="n">
         <v>78.73510653663386</v>
       </c>
       <c r="J66" t="n">
-        <v>13.87474822963421</v>
+        <v>9.118168597989158</v>
       </c>
       <c r="K66" t="n">
         <v>78.73510653663386</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>2.390025984754244</v>
+        <v>78.73510653663386</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>2.390025984754244</v>
+        <v>78.73510653663386</v>
       </c>
     </row>
     <row r="73">
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>4.047794627837633</v>
+        <v>78.73510653663386</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>4.047794627837633</v>
+        <v>78.73510653663386</v>
       </c>
     </row>
     <row r="74">
@@ -3182,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>5.328841591202335</v>
+        <v>78.73510653663386</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>5.328841591202335</v>
+        <v>78.73510653663386</v>
       </c>
     </row>
     <row r="75">
@@ -3219,13 +3219,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>6.370334719957311</v>
+        <v>78.73510653663386</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>6.370334719957311</v>
+        <v>78.73510653663386</v>
       </c>
     </row>
     <row r="76">
@@ -3256,13 +3256,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>7.244528179392905</v>
+        <v>78.73510653663386</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>7.244528179392905</v>
+        <v>78.73510653663386</v>
       </c>
     </row>
     <row r="77">
@@ -3293,13 +3293,13 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>2.390025984754244</v>
+        <v>78.73510653663386</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>2.390025984754244</v>
+        <v>78.73510653663386</v>
       </c>
     </row>
     <row r="78">
@@ -3330,13 +3330,13 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>4.047794627837633</v>
+        <v>78.73510653663386</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>4.047794627837633</v>
+        <v>78.73510653663386</v>
       </c>
     </row>
     <row r="79">
@@ -3367,13 +3367,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>5.328841591202335</v>
+        <v>78.73510653663386</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>5.328841591202335</v>
+        <v>78.73510653663386</v>
       </c>
     </row>
     <row r="80">
@@ -3404,13 +3404,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>6.370334719957311</v>
+        <v>78.73510653663386</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>6.370334719957311</v>
+        <v>78.73510653663386</v>
       </c>
     </row>
     <row r="81">
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>7.244528179392905</v>
+        <v>78.73510653663386</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>7.244528179392905</v>
+        <v>78.73510653663386</v>
       </c>
     </row>
     <row r="82">
